--- a/data/trans_orig/IP22D3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Clase-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37108</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46604</t>
+          <t>46459</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>82109</t>
+          <t>81775</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>93877</t>
+          <t>94210</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,47 +720,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6287</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6266</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>44,75%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,82 +1289,82 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,27 +1477,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,69 +1863,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2290</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>35,56%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3028</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>44,71%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,47 +2427,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>421</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -2540,74 +2540,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14609</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10229</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16869</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>82,08%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>57,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>17478</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15068</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>11818</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>77,62%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>16776</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>11974</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>19318</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>39</t>
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -2653,82 +2653,82 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3109,64 +3109,64 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>10575</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>13083</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3678,64 +3678,64 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>13094</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>6359</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>40483</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>34202</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>44521</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>84,25%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>44630</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>41068</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>46459</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>89330</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>81775</t>
+          <t>73734</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>94210</t>
+          <t>84653</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -4360,82 +4360,82 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4768</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
